--- a/Data/JobChange/Workday_JobChange_Czechia.xlsx
+++ b/Data/JobChange/Workday_JobChange_Czechia.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A33AB83-851F-41EB-90F3-E2847E9FE71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC6F4D08-AE99-4690-89FF-3E0FD670B984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="79">
   <si>
     <t>Test_ID</t>
   </si>
@@ -133,15 +133,6 @@
     <t>Step</t>
   </si>
   <si>
-    <t>CollectiveAgreement</t>
-  </si>
-  <si>
-    <t>ProfessionalCategory</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
     <t>Test_1</t>
   </si>
   <si>
@@ -181,15 +172,6 @@
     <t>Auto 74178418</t>
   </si>
   <si>
-    <t>Collective Agreement - Slovenia (01/01/1900 - )</t>
-  </si>
-  <si>
-    <t>Asistent v prodaji</t>
-  </si>
-  <si>
-    <t>IV.</t>
-  </si>
-  <si>
     <t>Test_2</t>
   </si>
   <si>
@@ -242,9 +224,6 @@
   </si>
   <si>
     <t>Harvey</t>
-  </si>
-  <si>
-    <t>10700311</t>
   </si>
   <si>
     <t>Test_5</t>
@@ -273,9 +252,6 @@
   </si>
   <si>
     <t>Rippin</t>
-  </si>
-  <si>
-    <t>10700312</t>
   </si>
   <si>
     <t>Test_7</t>
@@ -345,7 +321,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -361,12 +337,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -456,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -468,20 +438,17 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -489,17 +456,15 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -507,7 +472,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -825,7 +790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AK9"/>
+  <dimension ref="A1:AH9"/>
   <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.08984375" customWidth="1"/>
@@ -861,11 +826,9 @@
     <col min="31" max="31" width="32.36328125" customWidth="1"/>
     <col min="32" max="32" width="33.54296875" customWidth="1"/>
     <col min="33" max="34" width="42.54296875" customWidth="1"/>
-    <col min="35" max="35" width="18.26953125" customWidth="1"/>
-    <col min="36" max="36" width="18.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -968,904 +931,827 @@
       <c r="AH1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:34" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="B2" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="5" t="s">
+      <c r="C2" t="s">
         <v>36</v>
       </c>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="7">
+        <v>10700307</v>
+      </c>
+      <c r="H2" s="8">
+        <v>45870</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" s="10">
+        <v>895</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="P2" s="10">
+        <v>895</v>
+      </c>
+      <c r="Q2" s="9">
+        <v>40</v>
+      </c>
+      <c r="R2" s="10">
+        <v>5</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="T2" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="U2" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="W2" s="10">
+        <v>40</v>
+      </c>
+      <c r="X2" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA2" s="10">
+        <v>92</v>
+      </c>
+      <c r="AB2" s="10">
+        <v>251</v>
+      </c>
+      <c r="AC2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG2" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH2" s="10" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="2" spans="1:37" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:34" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" t="s">
         <v>37</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E3" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="8">
+        <v>45870</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L3" s="10">
+        <v>895</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="P3" s="10">
+        <v>895</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>40</v>
+      </c>
+      <c r="R3" s="10">
+        <v>5</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="T3" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="U3" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="V3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="W3" s="10">
+        <v>40</v>
+      </c>
+      <c r="X3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA3" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB3" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH3" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="8">
-        <v>10700307</v>
-      </c>
-      <c r="H2" s="9">
-        <v>45870</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" s="11" t="s">
+      <c r="G4" s="1">
+        <v>10700345</v>
+      </c>
+      <c r="H4" s="8">
+        <v>45901</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="P4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>25</v>
+      </c>
+      <c r="R4" s="10">
+        <v>5</v>
+      </c>
+      <c r="S4" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="T4" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="K2" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="L2" s="11">
-        <v>895</v>
-      </c>
-      <c r="M2" s="11" t="s">
+      <c r="U4" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="V4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="W4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="X4" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH4" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5" s="1">
+        <v>10700347</v>
+      </c>
+      <c r="H5" s="8">
+        <v>45901</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="R5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="T5" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="N2" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="P2" s="11">
-        <v>895</v>
-      </c>
-      <c r="Q2" s="10">
-        <v>40</v>
-      </c>
-      <c r="R2" s="11">
-        <v>5</v>
-      </c>
-      <c r="S2" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="T2" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="U2" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="V2" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="W2" s="11">
-        <v>40</v>
-      </c>
-      <c r="X2" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y2" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA2" s="11">
-        <v>92</v>
-      </c>
-      <c r="AB2" s="11">
-        <v>251</v>
-      </c>
-      <c r="AC2" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD2" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE2" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF2" s="11" t="s">
+      <c r="U5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="V5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="W5" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="X5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG5" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH5" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="AG2" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH2" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI2" s="16" t="s">
+      <c r="F6" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="AJ2" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK2" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H3" s="9">
-        <v>45870</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="K3" s="12" t="s">
+      <c r="G6" s="1">
+        <v>10700348</v>
+      </c>
+      <c r="H6" s="8">
+        <v>45931</v>
+      </c>
+      <c r="I6" t="s">
         <v>59</v>
       </c>
-      <c r="L3" s="11">
-        <v>895</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="P3" s="11">
-        <v>895</v>
-      </c>
-      <c r="Q3" s="10">
-        <v>40</v>
-      </c>
-      <c r="R3" s="11">
-        <v>5</v>
-      </c>
-      <c r="S3" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="T3" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="U3" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="V3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="W3" s="11">
-        <v>40</v>
-      </c>
-      <c r="X3" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA3" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB3" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI3" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ3" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK3" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="8">
-        <v>10700307</v>
-      </c>
-      <c r="H4" s="9">
-        <v>45901</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="N4" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="O4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="P4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q4" s="10">
-        <v>25</v>
-      </c>
-      <c r="R4" s="11">
-        <v>5</v>
-      </c>
-      <c r="S4" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="T4" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="U4" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="V4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="W4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="X4" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI4" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ4" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK4" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:37" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="J6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6" t="s">
+        <v>41</v>
+      </c>
+      <c r="O6" t="s">
+        <v>41</v>
+      </c>
+      <c r="P6" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>41</v>
+      </c>
+      <c r="R6" t="s">
+        <v>41</v>
+      </c>
+      <c r="S6" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="T6" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="H5" s="9">
-        <v>45901</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="N5" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="O5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="P5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q5" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="R5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="S5" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="T5" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="U5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="V5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="W5" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="X5" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI5" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ5" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK5" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:37" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="9">
-        <v>45931</v>
-      </c>
-      <c r="I6" t="s">
-        <v>65</v>
-      </c>
-      <c r="J6" t="s">
-        <v>44</v>
-      </c>
-      <c r="K6" t="s">
-        <v>44</v>
-      </c>
-      <c r="L6" t="s">
-        <v>44</v>
-      </c>
-      <c r="M6" t="s">
-        <v>44</v>
-      </c>
-      <c r="N6" t="s">
-        <v>44</v>
-      </c>
-      <c r="O6" t="s">
-        <v>44</v>
-      </c>
-      <c r="P6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>44</v>
-      </c>
-      <c r="R6" t="s">
-        <v>44</v>
-      </c>
-      <c r="S6" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="T6" s="21" t="s">
-        <v>75</v>
-      </c>
       <c r="U6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="V6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="W6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X6" s="22">
+        <v>41</v>
+      </c>
+      <c r="X6" s="19">
         <f>H6+364</f>
         <v>46295</v>
       </c>
       <c r="Y6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Z6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AA6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AB6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AC6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AD6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AE6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AF6" t="s">
-        <v>76</v>
-      </c>
-      <c r="AG6" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH6" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI6" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ6" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK6" s="17" t="s">
-        <v>52</v>
+        <v>69</v>
+      </c>
+      <c r="AG6" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH6" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:37" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:34" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>78</v>
+        <v>70</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="H7" s="9">
+        <v>37</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="1">
+        <v>10700360</v>
+      </c>
+      <c r="H7" s="8">
         <v>45870</v>
       </c>
       <c r="I7" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="O7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="P7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="R7" t="s">
-        <v>44</v>
-      </c>
-      <c r="S7" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="T7" s="21" t="s">
-        <v>75</v>
+        <v>41</v>
+      </c>
+      <c r="S7" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="T7" s="18" t="s">
+        <v>68</v>
       </c>
       <c r="U7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="V7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="W7" t="s">
-        <v>44</v>
-      </c>
-      <c r="X7" s="22">
+        <v>41</v>
+      </c>
+      <c r="X7" s="19">
         <f>H7+364</f>
         <v>46234</v>
       </c>
       <c r="Y7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Z7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AA7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AB7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AC7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AD7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AE7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AF7" t="s">
-        <v>76</v>
-      </c>
-      <c r="AG7" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH7" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI7" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ7" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK7" s="17" t="s">
-        <v>52</v>
+        <v>69</v>
+      </c>
+      <c r="AG7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH7" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:37" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:34" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="19"/>
+        <v>74</v>
+      </c>
+      <c r="B8" s="16"/>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="9">
+        <v>37</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="1">
+        <v>10700367</v>
+      </c>
+      <c r="H8" s="8">
         <v>45828</v>
       </c>
       <c r="I8" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="O8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="P8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Q8">
         <v>40</v>
       </c>
       <c r="R8" t="s">
-        <v>84</v>
-      </c>
-      <c r="S8" s="13" t="s">
-        <v>44</v>
+        <v>76</v>
+      </c>
+      <c r="S8" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="T8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="U8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="V8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="W8">
         <v>40</v>
       </c>
       <c r="X8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Y8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Z8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AA8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AB8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AC8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AD8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AE8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AF8" t="s">
-        <v>76</v>
-      </c>
-      <c r="AG8" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH8" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI8" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ8" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK8" s="17" t="s">
-        <v>52</v>
+        <v>69</v>
+      </c>
+      <c r="AG8" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH8" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:37" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:34" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" s="19"/>
+        <v>77</v>
+      </c>
+      <c r="B9" s="16"/>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="9">
+        <v>37</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="1">
+        <v>10700369</v>
+      </c>
+      <c r="H9" s="8">
         <v>45926</v>
       </c>
       <c r="I9" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M9" t="s">
-        <v>44</v>
-      </c>
-      <c r="N9" s="23" t="s">
-        <v>86</v>
+        <v>41</v>
+      </c>
+      <c r="N9" s="20" t="s">
+        <v>78</v>
       </c>
       <c r="O9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="P9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Q9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="R9" t="s">
-        <v>44</v>
-      </c>
-      <c r="S9" s="13" t="s">
-        <v>44</v>
+        <v>41</v>
+      </c>
+      <c r="S9" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="T9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="U9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="V9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="W9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="X9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Y9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="Z9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AA9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AB9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AC9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AD9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AE9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AF9" t="s">
-        <v>76</v>
-      </c>
-      <c r="AG9" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH9" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI9" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ9" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK9" s="17" t="s">
-        <v>52</v>
+        <v>69</v>
+      </c>
+      <c r="AG9" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH9" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1881,37 +1767,37 @@
   <sheetData>
     <row r="1" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D2" s="24" t="s">
-        <v>83</v>
+      <c r="D2" s="21" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D3" s="25" t="s">
-        <v>64</v>
+      <c r="D3" s="22" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D4" s="25" t="s">
-        <v>54</v>
+      <c r="D4" s="22" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D5" s="26" t="s">
-        <v>43</v>
+      <c r="D5" s="23" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D6" s="26" t="s">
-        <v>74</v>
+      <c r="D6" s="23" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D7" s="26" t="s">
-        <v>68</v>
+      <c r="D7" s="23" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
